--- a/PC Macro Test.xlsx
+++ b/PC Macro Test.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fintru-my.sharepoint.com/personal/daniel_marquess_fintru_com/Documents/Documents/Talent Pool/Python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="136" documentId="8_{594C07D0-44E4-43AA-94C1-B0DD1B82AB84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C384C694-D023-4BC5-AE55-FF02FED2D6FA}"/>
+  <xr:revisionPtr revIDLastSave="319" documentId="8_{594C07D0-44E4-43AA-94C1-B0DD1B82AB84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C043C130-BC70-4239-A989-D894686BEB92}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{7D18F49D-3760-4239-9878-5DED59F96984}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{7D18F49D-3760-4239-9878-5DED59F96984}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1 (2)" sheetId="3" r:id="rId1"/>
     <sheet name="Sheet2 (2)" sheetId="4" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="170">
   <si>
     <t>PC</t>
   </si>
@@ -101,12 +102,6 @@
     <t>Expert</t>
   </si>
   <si>
-    <t>Lore 1</t>
-  </si>
-  <si>
-    <t>Lore 2</t>
-  </si>
-  <si>
     <t>Deception</t>
   </si>
   <si>
@@ -209,24 +204,9 @@
     <t>Instant Death</t>
   </si>
   <si>
-    <t>2+</t>
-  </si>
-  <si>
-    <t>1.5 &lt; 2</t>
-  </si>
-  <si>
-    <t>0.5 &lt; 1.5</t>
-  </si>
-  <si>
-    <t>&lt;0.5</t>
-  </si>
-  <si>
     <t>Starting Dying</t>
   </si>
   <si>
-    <t>HP Proportion</t>
-  </si>
-  <si>
     <t>Sane</t>
   </si>
   <si>
@@ -303,6 +283,273 @@
   </si>
   <si>
     <t>ID Heal Check</t>
+  </si>
+  <si>
+    <t>&lt;1</t>
+  </si>
+  <si>
+    <t>&lt;2</t>
+  </si>
+  <si>
+    <t>&lt;3</t>
+  </si>
+  <si>
+    <t>&lt;4</t>
+  </si>
+  <si>
+    <t>Threshold</t>
+  </si>
+  <si>
+    <t>MAX(ancestryHP, level) + CON</t>
+  </si>
+  <si>
+    <t>Death Check</t>
+  </si>
+  <si>
+    <t>Wound</t>
+  </si>
+  <si>
+    <t>Serious</t>
+  </si>
+  <si>
+    <t>Severe</t>
+  </si>
+  <si>
+    <t>Critical</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Society</t>
+  </si>
+  <si>
+    <t>Thievery</t>
+  </si>
+  <si>
+    <t>Survival</t>
+  </si>
+  <si>
+    <t>Medicine</t>
+  </si>
+  <si>
+    <t>Acrobatics</t>
+  </si>
+  <si>
+    <t>Athletics</t>
+  </si>
+  <si>
+    <t>Intimidation</t>
+  </si>
+  <si>
+    <t>Diplomacy</t>
+  </si>
+  <si>
+    <t>Lore_1</t>
+  </si>
+  <si>
+    <t>Lore_2</t>
+  </si>
+  <si>
+    <t>Class</t>
+  </si>
+  <si>
+    <t>Cleric</t>
+  </si>
+  <si>
+    <t>Fighter</t>
+  </si>
+  <si>
+    <t>Rogue</t>
+  </si>
+  <si>
+    <t>Purchase</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>Retraining: Combat Grab</t>
+  </si>
+  <si>
+    <t>Retraining: Wheeling Grab</t>
+  </si>
+  <si>
+    <t>Time Required</t>
+  </si>
+  <si>
+    <t>1 Week</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Cheetah Elixir</t>
+  </si>
+  <si>
+    <t>Dakvision Elixir</t>
+  </si>
+  <si>
+    <t>+2 Potency Rune</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>If available</t>
+  </si>
+  <si>
+    <t>Astral Property Rune</t>
+  </si>
+  <si>
+    <t>Resilient Fundamental Rune</t>
+  </si>
+  <si>
+    <t>Shadow Property Rune (Greater)</t>
+  </si>
+  <si>
+    <t>Dakvision Elixir (Moderate)</t>
+  </si>
+  <si>
+    <t>Cheetah Elixir (Greater)</t>
+  </si>
+  <si>
+    <t>Heartstone</t>
+  </si>
+  <si>
+    <t>Carried</t>
+  </si>
+  <si>
+    <t>Current Share</t>
+  </si>
+  <si>
+    <t>Boat Treasure</t>
+  </si>
+  <si>
+    <t>Books</t>
+  </si>
+  <si>
+    <t>Bonus</t>
+  </si>
+  <si>
+    <t>Grab (claws)</t>
+  </si>
+  <si>
+    <t>DC</t>
+  </si>
+  <si>
+    <t>Damage</t>
+  </si>
+  <si>
+    <t>Attack (claws)</t>
+  </si>
+  <si>
+    <t>18 =7(2d6)+11(5+2+4)</t>
+  </si>
+  <si>
+    <t>24 = 9(2d8) + 15(5+2+8)</t>
+  </si>
+  <si>
+    <t>Attack (kick)</t>
+  </si>
+  <si>
+    <t>With Astral</t>
+  </si>
+  <si>
+    <t>21.5 =7(2d6)+11(5+2+4) + 3.5(1d6)</t>
+  </si>
+  <si>
+    <t>27.5 = 9(2d8) + 15(5+2+8) + 3.5(1d6)</t>
+  </si>
+  <si>
+    <t>Starting Gold</t>
+  </si>
+  <si>
+    <t>Start</t>
+  </si>
+  <si>
+    <t>Total from Sales</t>
+  </si>
+  <si>
+    <t>Loot Share</t>
+  </si>
+  <si>
+    <t>Party Size</t>
+  </si>
+  <si>
+    <t>Total after Sales</t>
+  </si>
+  <si>
+    <t>Per PC (4)</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Per PC (5)</t>
+  </si>
+  <si>
+    <t>Desired Cost</t>
+  </si>
+  <si>
+    <t>Remaining</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Total Value</t>
+  </si>
+  <si>
+    <t>Item / Service</t>
+  </si>
+  <si>
+    <t>Buy?</t>
+  </si>
+  <si>
+    <t>Book</t>
+  </si>
+  <si>
+    <t>Posh goods</t>
+  </si>
+  <si>
+    <t>5 gp max each</t>
+  </si>
+  <si>
+    <t>Gold Bar</t>
+  </si>
+  <si>
+    <t>Arsenic</t>
+  </si>
+  <si>
+    <t>Instant</t>
+  </si>
+  <si>
+    <t>Gold Nugget</t>
+  </si>
+  <si>
+    <t>Mithril Chunks</t>
+  </si>
+  <si>
+    <t>1 claimed by Belvis</t>
+  </si>
+  <si>
+    <t>TBC</t>
+  </si>
+  <si>
+    <t>Silver Ingots</t>
+  </si>
+  <si>
+    <t>Claimed by Nagol</t>
   </si>
 </sst>
 </file>
@@ -353,7 +600,14 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -364,6 +618,37 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DB945006-7FF8-49AE-A384-EC45330AF33A}" name="Goods_to_Sell" displayName="Goods_to_Sell" ref="A8:E15" totalsRowShown="0">
+  <autoFilter ref="A8:E15" xr:uid="{DB945006-7FF8-49AE-A384-EC45330AF33A}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{FD4A1CF8-9C27-4EDD-8C6F-DCE57E5FC9B6}" name="Item"/>
+    <tableColumn id="2" xr3:uid="{8EED26F4-D313-4E40-A305-5C82EA73D2E3}" name="Value"/>
+    <tableColumn id="3" xr3:uid="{03FECED4-76CE-49E7-B2C3-5ADB722E6FB4}" name="Quantity"/>
+    <tableColumn id="4" xr3:uid="{CE080ACC-BC26-458B-B99F-7F53B5B35193}" name="Total Value" dataDxfId="1">
+      <calculatedColumnFormula>Goods_to_Sell[[#This Row],[Value]]*Goods_to_Sell[[#This Row],[Quantity]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{1661854E-F145-4B03-BF0F-5DF60A5DF331}" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E5800A37-1A50-492F-BD2F-ACE5426323F1}" name="item_services" displayName="item_services" ref="H8:K18" totalsRowShown="0">
+  <autoFilter ref="H8:K18" xr:uid="{E5800A37-1A50-492F-BD2F-ACE5426323F1}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{4009898A-AA0F-4AFC-9510-50860536AD06}" name="Item / Service"/>
+    <tableColumn id="2" xr3:uid="{64A20CBD-912A-4BA7-8BF5-8BB675396CF1}" name="Cost"/>
+    <tableColumn id="3" xr3:uid="{591C28BB-9423-49F5-A35D-35EFA74361BE}" name="Time Required"/>
+    <tableColumn id="4" xr3:uid="{368950BE-CD40-40B9-8859-EB3BC346D423}" name="Buy?" dataDxfId="0">
+      <calculatedColumnFormula>TRUE</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -686,23 +971,32 @@
   <dimension ref="A1:J25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B2">
         <v>4</v>
@@ -716,7 +1010,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -730,7 +1024,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -741,21 +1035,21 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C10">
         <f>SUM(C12:C1048576)</f>
         <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E10">
         <f>SUM(E12:E1048576)</f>
         <v>3</v>
       </c>
       <c r="F10" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G10">
         <f>SUM(G12:G1048576)</f>
@@ -764,39 +1058,39 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F11" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C12">
         <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -804,19 +1098,19 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -824,13 +1118,13 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D14" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -838,7 +1132,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -846,27 +1140,27 @@
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H21" s="2">
         <v>2816.67</v>
@@ -878,7 +1172,7 @@
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H22">
         <f>H21*12</f>
@@ -916,7 +1210,7 @@
   <dimension ref="A1:R27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="9" width="14.44140625" customWidth="1"/>
@@ -925,43 +1219,43 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B1" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C1" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" t="s">
         <v>71</v>
       </c>
-      <c r="E1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F1" t="s">
-        <v>78</v>
-      </c>
       <c r="G1" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="H1" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="I1" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="J1" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="K1" t="s">
-        <v>76</v>
-      </c>
-      <c r="L1" t="s">
         <v>69</v>
       </c>
       <c r="M1" t="s">
-        <v>68</v>
+        <v>62</v>
+      </c>
+      <c r="N1" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -982,14 +1276,14 @@
         <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G2">
         <f>ROUNDDOWN(D2,0)+1</f>
         <v>7</v>
       </c>
       <c r="H2" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I2">
         <v>25</v>
@@ -1000,11 +1294,11 @@
       <c r="K2">
         <v>15</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="M2" t="s">
-        <v>74</v>
+      <c r="N2" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
@@ -1025,14 +1319,14 @@
         <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G3">
         <f>ROUNDDOWN(D3,0)+1</f>
         <v>13</v>
       </c>
       <c r="H3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="I3">
         <v>35</v>
@@ -1043,11 +1337,11 @@
       <c r="K3">
         <v>25</v>
       </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3" t="s">
-        <v>67</v>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
@@ -1068,14 +1362,14 @@
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G4">
         <f>ROUNDDOWN(D4,0)+1</f>
         <v>17</v>
       </c>
       <c r="H4" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I4">
         <v>45</v>
@@ -1086,11 +1380,11 @@
       <c r="K4">
         <v>35</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>2</v>
       </c>
-      <c r="M4" t="s">
-        <v>64</v>
+      <c r="N4" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
@@ -1111,14 +1405,14 @@
         <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="G5">
         <f>ROUNDDOWN(D5,0)</f>
         <v>20</v>
       </c>
       <c r="H5" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I5">
         <v>55</v>
@@ -1129,66 +1423,78 @@
       <c r="K5">
         <v>45</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>3</v>
       </c>
-      <c r="M5" t="s">
-        <v>66</v>
+      <c r="N5" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="L6">
+      <c r="M6">
         <v>4</v>
       </c>
-      <c r="M6" t="s">
-        <v>65</v>
+      <c r="N6" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="L7">
+      <c r="M7">
         <v>5</v>
       </c>
-      <c r="M7" t="s">
-        <v>63</v>
+      <c r="N7" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="L8">
+      <c r="M8">
         <v>6</v>
       </c>
-      <c r="M8" t="s">
-        <v>62</v>
+      <c r="N8" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>85</v>
+      </c>
+      <c r="C9" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B10">
+      <c r="A10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>58</v>
-      </c>
-      <c r="B11">
+        <v>89</v>
+      </c>
+      <c r="B11" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11">
         <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B12">
+        <v>90</v>
+      </c>
+      <c r="B12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12">
         <v>3</v>
       </c>
       <c r="F12">
@@ -1197,10 +1503,13 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="B13" t="s">
-        <v>55</v>
+        <v>84</v>
+      </c>
+      <c r="C13">
+        <v>4</v>
       </c>
       <c r="F13">
         <v>13</v>
@@ -1264,7 +1573,7 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M16">
         <v>2</v>
@@ -1292,10 +1601,13 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B17">
         <v>2</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
       </c>
       <c r="M17">
         <v>1</v>
@@ -1323,87 +1635,154 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="E18" t="s">
+        <v>88</v>
+      </c>
+      <c r="F18">
+        <f ca="1">RANDBETWEEN(1,4)</f>
+        <v>4</v>
+      </c>
+      <c r="G18">
+        <f t="shared" ref="G18:J18" ca="1" si="3">RANDBETWEEN(1,4)</f>
+        <v>4</v>
+      </c>
+      <c r="H18">
+        <f t="shared" ca="1" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="I18">
+        <f t="shared" ca="1" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="J18">
+        <f t="shared" ca="1" si="3"/>
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B19">
         <v>0</v>
       </c>
+      <c r="C19">
+        <v>3</v>
+      </c>
+      <c r="E19" t="s">
+        <v>87</v>
+      </c>
       <c r="F19">
-        <f t="shared" ref="F19:I19" ca="1" si="3">RANDBETWEEN(1,20)</f>
+        <f t="shared" ref="F19:J19" ca="1" si="4">RANDBETWEEN(1,20)</f>
+        <v>2</v>
+      </c>
+      <c r="G19">
+        <f t="shared" ca="1" si="4"/>
         <v>10</v>
       </c>
-      <c r="G19">
-        <f t="shared" ca="1" si="3"/>
-        <v>12</v>
-      </c>
       <c r="H19">
-        <f t="shared" ca="1" si="3"/>
-        <v>20</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>4</v>
       </c>
       <c r="I19">
-        <f t="shared" ca="1" si="3"/>
-        <v>18</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>7</v>
       </c>
       <c r="J19">
-        <f ca="1">RANDBETWEEN(1,20)</f>
-        <v>20</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
+      <c r="C20">
+        <v>4</v>
+      </c>
+      <c r="E20" t="s">
+        <v>52</v>
+      </c>
       <c r="F20">
-        <f t="shared" ref="F20:I20" ca="1" si="4">RANDBETWEEN(1,6)</f>
-        <v>4</v>
+        <f t="shared" ref="F20:J21" ca="1" si="5">RANDBETWEEN(1,6)</f>
+        <v>1</v>
       </c>
       <c r="G20">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>3</v>
       </c>
       <c r="H20">
-        <f t="shared" ca="1" si="4"/>
-        <v>6</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>1</v>
       </c>
       <c r="I20">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>5</v>
       </c>
       <c r="J20">
-        <f ca="1">RANDBETWEEN(1,6)</f>
-        <v>1</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B21">
         <v>-1</v>
       </c>
+      <c r="C21">
+        <v>5</v>
+      </c>
+      <c r="E21" t="s">
+        <v>61</v>
+      </c>
+      <c r="F21">
+        <f t="shared" ca="1" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="G21">
+        <f t="shared" ca="1" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="H21">
+        <f t="shared" ca="1" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="I21">
+        <f t="shared" ca="1" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="J21">
+        <f t="shared" ca="1" si="5"/>
+        <v>2</v>
+      </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B22">
         <v>-1</v>
       </c>
+      <c r="C22">
+        <v>6</v>
+      </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -1411,7 +1790,7 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -1419,7 +1798,7 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B27">
         <v>-1</v>
@@ -1432,88 +1811,116 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2DFA59F-F097-4A2D-B134-58CB1563E26C}">
-  <dimension ref="A1:T17"/>
+  <dimension ref="A1:Z28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.88671875" customWidth="1"/>
-    <col min="12" max="13" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5546875" customWidth="1"/>
+    <col min="3" max="3" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.88671875" customWidth="1"/>
+    <col min="13" max="14" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>103</v>
       </c>
       <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
-        <v>22</v>
-      </c>
       <c r="L1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>11</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" t="s">
-        <v>20</v>
-      </c>
       <c r="Q1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+        <v>93</v>
+      </c>
+      <c r="R1" t="s">
+        <v>94</v>
+      </c>
+      <c r="S1" t="s">
+        <v>95</v>
+      </c>
+      <c r="T1" t="s">
+        <v>96</v>
+      </c>
+      <c r="U1" t="s">
+        <v>97</v>
+      </c>
+      <c r="V1" t="s">
+        <v>98</v>
+      </c>
+      <c r="W1" t="s">
+        <v>99</v>
+      </c>
+      <c r="X1" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>16</v>
       </c>
-      <c r="B2">
-        <v>1</v>
+      <c r="B2" t="s">
+        <v>104</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2">
         <v>2</v>
@@ -1522,22 +1929,22 @@
         <v>2</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
         <v>4</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>0</v>
-      </c>
-      <c r="I2" t="s">
-        <v>15</v>
       </c>
       <c r="J2" t="s">
         <v>15</v>
       </c>
       <c r="K2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L2" t="s">
         <v>14</v>
@@ -1549,7 +1956,7 @@
         <v>14</v>
       </c>
       <c r="O2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P2" t="s">
         <v>15</v>
@@ -1557,37 +1964,64 @@
       <c r="Q2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" t="s">
+        <v>14</v>
+      </c>
+      <c r="T2" t="s">
+        <v>14</v>
+      </c>
+      <c r="U2" t="s">
+        <v>14</v>
+      </c>
+      <c r="V2" t="s">
+        <v>14</v>
+      </c>
+      <c r="W2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3">
-        <v>1</v>
+      <c r="B3" t="s">
+        <v>105</v>
       </c>
       <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
         <v>4</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>2</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>3</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>0</v>
       </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
       <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>15</v>
-      </c>
-      <c r="J3" t="s">
-        <v>14</v>
       </c>
       <c r="K3" t="s">
         <v>14</v>
@@ -1596,76 +2030,281 @@
         <v>14</v>
       </c>
       <c r="M3" t="s">
+        <v>14</v>
+      </c>
+      <c r="N3" t="s">
         <v>15</v>
-      </c>
-      <c r="N3" t="s">
-        <v>14</v>
       </c>
       <c r="O3" t="s">
         <v>14</v>
       </c>
       <c r="P3" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q3" t="s">
         <v>15</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S3" t="s">
+        <v>14</v>
+      </c>
+      <c r="T3" t="s">
+        <v>14</v>
+      </c>
+      <c r="U3" t="s">
+        <v>15</v>
+      </c>
+      <c r="V3" t="s">
+        <v>14</v>
+      </c>
+      <c r="W3" t="s">
+        <v>14</v>
+      </c>
+      <c r="X3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
-      <c r="B4">
-        <v>1</v>
+      <c r="B4" t="s">
+        <v>106</v>
       </c>
       <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
         <v>2</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>4</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4">
         <v>2</v>
       </c>
-      <c r="I4" t="s">
-        <v>19</v>
+      <c r="I4">
+        <v>2</v>
       </c>
       <c r="J4" t="s">
         <v>19</v>
       </c>
       <c r="K4" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L4" t="s">
         <v>15</v>
       </c>
       <c r="M4" t="s">
+        <v>15</v>
+      </c>
+      <c r="N4" t="s">
         <v>14</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>15</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>14</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
+        <v>19</v>
+      </c>
+      <c r="R4" t="s">
+        <v>19</v>
+      </c>
+      <c r="S4" t="s">
         <v>15</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="T4" t="s">
+        <v>15</v>
+      </c>
+      <c r="U4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="17" spans="20:20" x14ac:dyDescent="0.3">
-      <c r="T17" s="1"/>
+      <c r="V4" t="s">
+        <v>15</v>
+      </c>
+      <c r="W4" t="s">
+        <v>14</v>
+      </c>
+      <c r="X4" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="C12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" t="str">
+        <f>_xlfn.CONCAT("'",C12,"': row['",C12,"'],")</f>
+        <v>'Perception': row['Perception'],</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="C13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" t="str">
+        <f t="shared" ref="D13:D28" si="0">_xlfn.CONCAT("'",C13,"': row['",C13,"'],")</f>
+        <v>'Stealth': row['Stealth'],</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="C14" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" t="str">
+        <f t="shared" si="0"/>
+        <v>'Deception': row['Deception'],</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="C15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" t="str">
+        <f t="shared" si="0"/>
+        <v>'Arcana': row['Arcana'],</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" t="str">
+        <f t="shared" si="0"/>
+        <v>'Nature': row['Nature'],</v>
+      </c>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" t="str">
+        <f t="shared" si="0"/>
+        <v>'Occultism': row['Occultism'],</v>
+      </c>
+      <c r="U17" s="1"/>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" t="str">
+        <f t="shared" si="0"/>
+        <v>'Religion': row['Religion'],</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C19" t="s">
+        <v>93</v>
+      </c>
+      <c r="D19" t="str">
+        <f t="shared" si="0"/>
+        <v>'Society': row['Society'],</v>
+      </c>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C20" t="s">
+        <v>94</v>
+      </c>
+      <c r="D20" t="str">
+        <f t="shared" si="0"/>
+        <v>'Thievery': row['Thievery'],</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C21" t="s">
+        <v>95</v>
+      </c>
+      <c r="D21" t="str">
+        <f t="shared" si="0"/>
+        <v>'Survival': row['Survival'],</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C22" t="s">
+        <v>96</v>
+      </c>
+      <c r="D22" t="str">
+        <f t="shared" si="0"/>
+        <v>'Medicine': row['Medicine'],</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C23" t="s">
+        <v>97</v>
+      </c>
+      <c r="D23" t="str">
+        <f t="shared" si="0"/>
+        <v>'Acrobatics': row['Acrobatics'],</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C24" t="s">
+        <v>98</v>
+      </c>
+      <c r="D24" t="str">
+        <f t="shared" si="0"/>
+        <v>'Athletics': row['Athletics'],</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C25" t="s">
+        <v>99</v>
+      </c>
+      <c r="D25" t="str">
+        <f t="shared" si="0"/>
+        <v>'Intimidation': row['Intimidation'],</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C26" t="s">
+        <v>100</v>
+      </c>
+      <c r="D26" t="str">
+        <f t="shared" si="0"/>
+        <v>'Diplomacy': row['Diplomacy'],</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C27" t="s">
+        <v>101</v>
+      </c>
+      <c r="D27" t="str">
+        <f t="shared" si="0"/>
+        <v>'Lore_1': row['Lore_1'],</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C28" t="s">
+        <v>102</v>
+      </c>
+      <c r="D28" t="str">
+        <f t="shared" si="0"/>
+        <v>'Lore_2': row['Lore_2'],</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1675,9 +2314,646 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1214124C-EE3E-4253-850B-62BC0EFDA621}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.6640625" customWidth="1"/>
+    <col min="8" max="8" width="12.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I2">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3">
+        <v>0.8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>113</v>
+      </c>
+      <c r="H3" t="s">
+        <v>127</v>
+      </c>
+      <c r="I3">
+        <f>(1430.5 / 4)-200</f>
+        <v>157.625</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>114</v>
+      </c>
+      <c r="H4" t="s">
+        <v>128</v>
+      </c>
+      <c r="I4">
+        <f>540/4</f>
+        <v>135</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5" t="s">
+        <v>114</v>
+      </c>
+      <c r="H5" t="s">
+        <v>129</v>
+      </c>
+      <c r="I5">
+        <f>180/4</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6">
+        <v>935</v>
+      </c>
+      <c r="E6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C7">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>121</v>
+      </c>
+      <c r="C8">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>122</v>
+      </c>
+      <c r="C9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>124</v>
+      </c>
+      <c r="C11">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>130</v>
+      </c>
+      <c r="C18" t="s">
+        <v>132</v>
+      </c>
+      <c r="D18" t="s">
+        <v>133</v>
+      </c>
+      <c r="E18" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B19">
+        <v>20</v>
+      </c>
+      <c r="D19" t="s">
+        <v>135</v>
+      </c>
+      <c r="E19" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>131</v>
+      </c>
+      <c r="B20">
+        <v>22</v>
+      </c>
+      <c r="C20">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>137</v>
+      </c>
+      <c r="B21">
+        <v>20</v>
+      </c>
+      <c r="D21" t="s">
+        <v>136</v>
+      </c>
+      <c r="E21" t="s">
+        <v>140</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96EF9FD7-06AC-4F6E-96C5-05EB0511350B}">
+  <dimension ref="A1:P19"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B1">
+        <v>1430.5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I1">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B2">
+        <f>SUM(D:D)</f>
+        <v>5420</v>
+      </c>
+      <c r="H2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I2">
+        <f>IF(L2=4,B4,B5)</f>
+        <v>1712.625</v>
+      </c>
+      <c r="K2" t="s">
+        <v>145</v>
+      </c>
+      <c r="L2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B3">
+        <f>B1+B2</f>
+        <v>6850.5</v>
+      </c>
+      <c r="H3" t="s">
+        <v>125</v>
+      </c>
+      <c r="I3">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B4">
+        <f>B3/4</f>
+        <v>1712.625</v>
+      </c>
+      <c r="H4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I4">
+        <f>SUM(I1:I3)</f>
+        <v>1517.925</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B5">
+        <f>B3/5</f>
+        <v>1370.1</v>
+      </c>
+      <c r="H5" t="s">
+        <v>150</v>
+      </c>
+      <c r="I5">
+        <f>SUMIF(item_services[Buy?], TRUE, item_services[Cost])</f>
+        <v>1492.8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H6" t="s">
+        <v>151</v>
+      </c>
+      <c r="I6">
+        <f>I4-I5</f>
+        <v>25.125</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>152</v>
+      </c>
+      <c r="B8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C8" t="s">
+        <v>154</v>
+      </c>
+      <c r="D8" t="s">
+        <v>155</v>
+      </c>
+      <c r="E8" t="s">
+        <v>118</v>
+      </c>
+      <c r="H8" t="s">
+        <v>156</v>
+      </c>
+      <c r="I8" t="s">
+        <v>108</v>
+      </c>
+      <c r="J8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K8" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>158</v>
+      </c>
+      <c r="B9">
+        <v>20</v>
+      </c>
+      <c r="C9">
+        <v>9</v>
+      </c>
+      <c r="D9">
+        <f>Goods_to_Sell[[#This Row],[Value]]*Goods_to_Sell[[#This Row],[Quantity]]</f>
+        <v>180</v>
+      </c>
+      <c r="H9" t="s">
+        <v>110</v>
+      </c>
+      <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="J9" t="s">
+        <v>113</v>
+      </c>
+      <c r="K9" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>159</v>
+      </c>
+      <c r="B10">
+        <v>540</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <f>Goods_to_Sell[[#This Row],[Value]]*Goods_to_Sell[[#This Row],[Quantity]]</f>
+        <v>540</v>
+      </c>
+      <c r="E10" t="s">
+        <v>160</v>
+      </c>
+      <c r="H10" t="s">
+        <v>111</v>
+      </c>
+      <c r="I10">
+        <v>0.8</v>
+      </c>
+      <c r="J10" t="s">
+        <v>113</v>
+      </c>
+      <c r="K10" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>161</v>
+      </c>
+      <c r="B11">
+        <v>1000</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <f>Goods_to_Sell[[#This Row],[Value]]*Goods_to_Sell[[#This Row],[Quantity]]</f>
+        <v>1000</v>
+      </c>
+      <c r="E11" t="s">
+        <v>162</v>
+      </c>
+      <c r="H11" t="s">
+        <v>116</v>
+      </c>
+      <c r="I11">
+        <v>11</v>
+      </c>
+      <c r="J11" t="s">
+        <v>163</v>
+      </c>
+      <c r="K11" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>164</v>
+      </c>
+      <c r="B12">
+        <v>50</v>
+      </c>
+      <c r="C12">
+        <v>20</v>
+      </c>
+      <c r="D12">
+        <f>Goods_to_Sell[[#This Row],[Value]]*Goods_to_Sell[[#This Row],[Quantity]]</f>
+        <v>1000</v>
+      </c>
+      <c r="E12" t="s">
+        <v>162</v>
+      </c>
+      <c r="H12" t="s">
+        <v>115</v>
+      </c>
+      <c r="I12">
+        <v>3</v>
+      </c>
+      <c r="J12" t="s">
+        <v>163</v>
+      </c>
+      <c r="K12" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>165</v>
+      </c>
+      <c r="B13">
+        <v>500</v>
+      </c>
+      <c r="C13">
+        <v>4</v>
+      </c>
+      <c r="D13">
+        <f>Goods_to_Sell[[#This Row],[Value]]*Goods_to_Sell[[#This Row],[Quantity]]</f>
+        <v>2000</v>
+      </c>
+      <c r="E13" t="s">
+        <v>166</v>
+      </c>
+      <c r="H13" t="s">
+        <v>120</v>
+      </c>
+      <c r="I13">
+        <v>450</v>
+      </c>
+      <c r="J13" t="s">
+        <v>167</v>
+      </c>
+      <c r="K13" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>168</v>
+      </c>
+      <c r="B14">
+        <v>100</v>
+      </c>
+      <c r="C14">
+        <v>5</v>
+      </c>
+      <c r="D14">
+        <f>Goods_to_Sell[[#This Row],[Value]]*Goods_to_Sell[[#This Row],[Quantity]]</f>
+        <v>500</v>
+      </c>
+      <c r="H14" t="s">
+        <v>121</v>
+      </c>
+      <c r="I14">
+        <v>340</v>
+      </c>
+      <c r="J14" t="s">
+        <v>167</v>
+      </c>
+      <c r="K14" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>125</v>
+      </c>
+      <c r="B15">
+        <v>200</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <f>Goods_to_Sell[[#This Row],[Value]]*Goods_to_Sell[[#This Row],[Quantity]]</f>
+        <v>200</v>
+      </c>
+      <c r="E15" t="s">
+        <v>169</v>
+      </c>
+      <c r="H15" t="s">
+        <v>122</v>
+      </c>
+      <c r="I15">
+        <v>650</v>
+      </c>
+      <c r="J15" t="s">
+        <v>167</v>
+      </c>
+      <c r="K15" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H16" t="s">
+        <v>123</v>
+      </c>
+      <c r="I16">
+        <v>11</v>
+      </c>
+      <c r="J16" t="s">
+        <v>163</v>
+      </c>
+      <c r="K16" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="8:16" x14ac:dyDescent="0.3">
+      <c r="H17" t="s">
+        <v>124</v>
+      </c>
+      <c r="I17">
+        <v>25</v>
+      </c>
+      <c r="J17" t="s">
+        <v>163</v>
+      </c>
+      <c r="K17" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="8:16" x14ac:dyDescent="0.3">
+      <c r="H18" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="I18">
+        <v>935</v>
+      </c>
+      <c r="J18" t="s">
+        <v>167</v>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="8:16" x14ac:dyDescent="0.3">
+      <c r="P19" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="2">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/PC Macro Test.xlsx
+++ b/PC Macro Test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fintru-my.sharepoint.com/personal/daniel_marquess_fintru_com/Documents/Documents/Talent Pool/Python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="319" documentId="8_{594C07D0-44E4-43AA-94C1-B0DD1B82AB84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C043C130-BC70-4239-A989-D894686BEB92}"/>
+  <xr:revisionPtr revIDLastSave="439" documentId="8_{594C07D0-44E4-43AA-94C1-B0DD1B82AB84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFAD1C97-F3B6-41B4-9812-63CC2B89A993}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{7D18F49D-3760-4239-9878-5DED59F96984}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="214">
   <si>
     <t>PC</t>
   </si>
@@ -550,6 +550,138 @@
   </si>
   <si>
     <t>Claimed by Nagol</t>
+  </si>
+  <si>
+    <t>Rolls</t>
+  </si>
+  <si>
+    <t>Crit Fail</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Success</t>
+  </si>
+  <si>
+    <t>Crit Success</t>
+  </si>
+  <si>
+    <t>Expectation</t>
+  </si>
+  <si>
+    <t>Size Changing</t>
+  </si>
+  <si>
+    <t>Sell Shadow Rune</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>For recap</t>
+  </si>
+  <si>
+    <t>Stranger</t>
+  </si>
+  <si>
+    <t>Rusted gear</t>
+  </si>
+  <si>
+    <t>Cursed disease</t>
+  </si>
+  <si>
+    <t>Many gifts</t>
+  </si>
+  <si>
+    <t>Coast dangerous</t>
+  </si>
+  <si>
+    <t>Points to emphaise in recap / convo</t>
+  </si>
+  <si>
+    <t>2 Brothers - could wait for the bridge, and just name them</t>
+  </si>
+  <si>
+    <t>2 bolts of strange non-surface material</t>
+  </si>
+  <si>
+    <t>Ragulf, reeve as drydock</t>
+  </si>
+  <si>
+    <t>3-4 Sand families</t>
+  </si>
+  <si>
+    <t>seasonal workers</t>
+  </si>
+  <si>
+    <t>red wind</t>
+  </si>
+  <si>
+    <t>encroaching empire - grumbling</t>
+  </si>
+  <si>
+    <t>Few off-islanders, primarily in the seasonal worker camp, or stranded merchants</t>
+  </si>
+  <si>
+    <t>Mistake the ship for military, it is more merchant navy</t>
+  </si>
+  <si>
+    <t>Recap</t>
+  </si>
+  <si>
+    <t>Bridge - explain VERY briefly the brother's story</t>
+  </si>
+  <si>
+    <t>3 minutes</t>
+  </si>
+  <si>
+    <t>&lt; 1 hour</t>
+  </si>
+  <si>
+    <t>Dero Ambush</t>
+  </si>
+  <si>
+    <t>&lt; 2 hours</t>
+  </si>
+  <si>
+    <t>Access Gate</t>
+  </si>
+  <si>
+    <t>&lt; 30 minutes</t>
+  </si>
+  <si>
+    <t>Describe Iron Harbour (MAP) - incl. lights of rusthenge? Definitely see the ship</t>
+  </si>
+  <si>
+    <t>Entering Iron Harbour - movement in the empty houses, on the beaches, streets locking down. Rust wind. Some food places in centre near the Drydock</t>
+  </si>
+  <si>
+    <t>Break off towards Hereswith's place or further ahead to the drydock</t>
+  </si>
+  <si>
+    <t>First encounter with Hereswith - acid test go boom, eager to haggle</t>
+  </si>
+  <si>
+    <t>First encounter with old architect, offers cheese and fish</t>
+  </si>
+  <si>
+    <t>First encounter with boatman - arguing with Sander family, then offer accomodation for fighting.</t>
+  </si>
+  <si>
+    <t>First encounter on ship - muscle head and acting captain</t>
+  </si>
+  <si>
+    <t>Boathouse follow up - fight club &amp; sabotage job offer</t>
+  </si>
+  <si>
+    <t>Ship follow up = Stonehome</t>
+  </si>
+  <si>
+    <t>Hereswith follow up - ram medicine, Stonehome, thefts</t>
+  </si>
+  <si>
+    <t>Architect follow up = Stonehome, thefts</t>
   </si>
 </sst>
 </file>
@@ -591,11 +723,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -620,6 +753,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DB945006-7FF8-49AE-A384-EC45330AF33A}" name="Goods_to_Sell" displayName="Goods_to_Sell" ref="A8:E15" totalsRowShown="0">
   <autoFilter ref="A8:E15" xr:uid="{DB945006-7FF8-49AE-A384-EC45330AF33A}"/>
@@ -637,9 +774,14 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E5800A37-1A50-492F-BD2F-ACE5426323F1}" name="item_services" displayName="item_services" ref="H8:K18" totalsRowShown="0">
-  <autoFilter ref="H8:K18" xr:uid="{E5800A37-1A50-492F-BD2F-ACE5426323F1}"/>
-  <tableColumns count="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E5800A37-1A50-492F-BD2F-ACE5426323F1}" name="item_services" displayName="item_services" ref="H8:L20" totalsRowShown="0">
+  <autoFilter ref="H8:L20" xr:uid="{E5800A37-1A50-492F-BD2F-ACE5426323F1}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H9:L20">
+    <sortCondition ref="H9:H18"/>
+    <sortCondition descending="1" ref="J9:J18"/>
+  </sortState>
+  <tableColumns count="5">
+    <tableColumn id="5" xr3:uid="{142A7124-A55A-4294-8DEA-62A55B6637EC}" name="Priority"/>
     <tableColumn id="1" xr3:uid="{4009898A-AA0F-4AFC-9510-50860536AD06}" name="Item / Service"/>
     <tableColumn id="2" xr3:uid="{64A20CBD-912A-4BA7-8BF5-8BB675396CF1}" name="Cost"/>
     <tableColumn id="3" xr3:uid="{591C28BB-9423-49F5-A35D-35EFA74361BE}" name="Time Required"/>
@@ -1648,23 +1790,23 @@
       </c>
       <c r="F18">
         <f ca="1">RANDBETWEEN(1,4)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G18">
         <f t="shared" ref="G18:J18" ca="1" si="3">RANDBETWEEN(1,4)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H18">
         <f t="shared" ca="1" si="3"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I18">
         <f t="shared" ca="1" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J18">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
@@ -1682,23 +1824,23 @@
       </c>
       <c r="F19">
         <f t="shared" ref="F19:J19" ca="1" si="4">RANDBETWEEN(1,20)</f>
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="G19">
         <f t="shared" ca="1" si="4"/>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H19">
         <f t="shared" ca="1" si="4"/>
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I19">
         <f t="shared" ca="1" si="4"/>
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J19">
         <f t="shared" ca="1" si="4"/>
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
@@ -1720,7 +1862,7 @@
       </c>
       <c r="G20">
         <f t="shared" ca="1" si="5"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H20">
         <f t="shared" ca="1" si="5"/>
@@ -1728,11 +1870,11 @@
       </c>
       <c r="I20">
         <f t="shared" ca="1" si="5"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J20">
         <f t="shared" ca="1" si="5"/>
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
@@ -1754,19 +1896,19 @@
       </c>
       <c r="G21">
         <f t="shared" ca="1" si="5"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H21">
         <f t="shared" ca="1" si="5"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I21">
         <f t="shared" ca="1" si="5"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J21">
         <f t="shared" ca="1" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
@@ -2557,7 +2699,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96EF9FD7-06AC-4F6E-96C5-05EB0511350B}">
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P59"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.77734375" bestFit="1" customWidth="1"/>
@@ -2565,12 +2707,14 @@
     <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>141</v>
       </c>
@@ -2584,20 +2728,20 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>143</v>
       </c>
       <c r="B2">
-        <f>SUM(D:D)</f>
-        <v>5420</v>
+        <f ca="1">SUM(D:D)</f>
+        <v>4877.5</v>
       </c>
       <c r="H2" t="s">
         <v>144</v>
       </c>
       <c r="I2">
-        <f>IF(L2=4,B4,B5)</f>
-        <v>1712.625</v>
+        <f ca="1">IF(L2=4,B4,B5)</f>
+        <v>1577</v>
       </c>
       <c r="K2" t="s">
         <v>145</v>
@@ -2606,13 +2750,13 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>146</v>
       </c>
       <c r="B3">
-        <f>B1+B2</f>
-        <v>6850.5</v>
+        <f ca="1">B1+B2</f>
+        <v>6308</v>
       </c>
       <c r="H3" t="s">
         <v>125</v>
@@ -2621,48 +2765,53 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>147</v>
       </c>
       <c r="B4">
-        <f>B3/4</f>
-        <v>1712.625</v>
+        <f ca="1">ROUND(B3/4,2)</f>
+        <v>1577</v>
       </c>
       <c r="H4" t="s">
         <v>148</v>
       </c>
       <c r="I4">
-        <f>SUM(I1:I3)</f>
-        <v>1517.925</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+        <f ca="1">SUM(I1:I3)</f>
+        <v>1382.3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>149</v>
       </c>
       <c r="B5">
-        <f>B3/5</f>
-        <v>1370.1</v>
+        <f ca="1">ROUND(B3/5,3)</f>
+        <v>1261.5999999999999</v>
       </c>
       <c r="H5" t="s">
         <v>150</v>
       </c>
       <c r="I5">
         <f>SUMIF(item_services[Buy?], TRUE, item_services[Cost])</f>
-        <v>1492.8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+        <v>1137.8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="H6" t="s">
         <v>151</v>
       </c>
       <c r="I6">
-        <f>I4-I5</f>
-        <v>25.125</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+        <f ca="1">I4-I5</f>
+        <v>244.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O7" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>152</v>
       </c>
@@ -2679,19 +2828,22 @@
         <v>118</v>
       </c>
       <c r="H8" t="s">
+        <v>109</v>
+      </c>
+      <c r="I8" t="s">
         <v>156</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>108</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>112</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>158</v>
       </c>
@@ -2705,21 +2857,24 @@
         <f>Goods_to_Sell[[#This Row],[Value]]*Goods_to_Sell[[#This Row],[Quantity]]</f>
         <v>180</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9" t="s">
         <v>110</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>2</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>113</v>
       </c>
-      <c r="K9" t="b">
+      <c r="L9" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>159</v>
       </c>
@@ -2736,21 +2891,24 @@
       <c r="E10" t="s">
         <v>160</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10" t="s">
         <v>111</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>0.8</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
         <v>113</v>
       </c>
-      <c r="K10" t="b">
+      <c r="L10" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>161</v>
       </c>
@@ -2767,21 +2925,24 @@
       <c r="E11" t="s">
         <v>162</v>
       </c>
-      <c r="H11" t="s">
-        <v>116</v>
-      </c>
-      <c r="I11">
-        <v>11</v>
-      </c>
-      <c r="J11" t="s">
-        <v>163</v>
-      </c>
-      <c r="K11" t="b">
+      <c r="H11">
+        <v>2</v>
+      </c>
+      <c r="I11" t="s">
+        <v>120</v>
+      </c>
+      <c r="J11">
+        <v>450</v>
+      </c>
+      <c r="K11" t="s">
+        <v>167</v>
+      </c>
+      <c r="L11" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>164</v>
       </c>
@@ -2798,21 +2959,21 @@
       <c r="E12" t="s">
         <v>162</v>
       </c>
-      <c r="H12" t="s">
-        <v>115</v>
-      </c>
-      <c r="I12">
-        <v>3</v>
-      </c>
-      <c r="J12" t="s">
-        <v>163</v>
-      </c>
-      <c r="K12" t="b">
+      <c r="H12">
+        <v>2</v>
+      </c>
+      <c r="I12" t="s">
+        <v>176</v>
+      </c>
+      <c r="J12">
+        <v>350</v>
+      </c>
+      <c r="L12" s="4" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>165</v>
       </c>
@@ -2820,30 +2981,30 @@
         <v>500</v>
       </c>
       <c r="C13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13">
         <f>Goods_to_Sell[[#This Row],[Value]]*Goods_to_Sell[[#This Row],[Quantity]]</f>
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="E13" t="s">
         <v>166</v>
       </c>
-      <c r="H13" t="s">
-        <v>120</v>
-      </c>
-      <c r="I13">
-        <v>450</v>
-      </c>
-      <c r="J13" t="s">
-        <v>167</v>
-      </c>
-      <c r="K13" t="b">
+      <c r="H13">
+        <v>2</v>
+      </c>
+      <c r="I13" t="s">
+        <v>177</v>
+      </c>
+      <c r="J13">
+        <v>-55</v>
+      </c>
+      <c r="L13" s="4" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>168</v>
       </c>
@@ -2857,21 +3018,24 @@
         <f>Goods_to_Sell[[#This Row],[Value]]*Goods_to_Sell[[#This Row],[Quantity]]</f>
         <v>500</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H14">
+        <v>3</v>
+      </c>
+      <c r="I14" t="s">
         <v>121</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>340</v>
       </c>
-      <c r="J14" t="s">
+      <c r="K14" t="s">
         <v>167</v>
       </c>
-      <c r="K14" t="b">
+      <c r="L14" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>125</v>
       </c>
@@ -2879,75 +3043,378 @@
         <v>200</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <f>Goods_to_Sell[[#This Row],[Value]]*Goods_to_Sell[[#This Row],[Quantity]]</f>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E15" t="s">
         <v>169</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H15">
+        <v>4</v>
+      </c>
+      <c r="I15" t="s">
+        <v>116</v>
+      </c>
+      <c r="J15">
+        <v>11</v>
+      </c>
+      <c r="K15" t="s">
+        <v>163</v>
+      </c>
+      <c r="L15" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="H16">
+        <v>4</v>
+      </c>
+      <c r="I16" t="s">
+        <v>115</v>
+      </c>
+      <c r="J16">
+        <v>3</v>
+      </c>
+      <c r="K16" t="s">
+        <v>163</v>
+      </c>
+      <c r="L16" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="H17">
+        <v>5</v>
+      </c>
+      <c r="I17" t="s">
+        <v>124</v>
+      </c>
+      <c r="J17">
+        <v>25</v>
+      </c>
+      <c r="K17" t="s">
+        <v>163</v>
+      </c>
+      <c r="L17" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C18" t="s">
+        <v>175</v>
+      </c>
+      <c r="D18">
+        <f>3.5*10</f>
+        <v>35</v>
+      </c>
+      <c r="H18">
+        <v>5</v>
+      </c>
+      <c r="I18" t="s">
+        <v>123</v>
+      </c>
+      <c r="J18">
+        <v>11</v>
+      </c>
+      <c r="K18" t="s">
+        <v>163</v>
+      </c>
+      <c r="L18" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C19" t="s">
+        <v>171</v>
+      </c>
+      <c r="D19">
+        <f ca="1">D20*2</f>
+        <v>70</v>
+      </c>
+      <c r="H19">
+        <v>6</v>
+      </c>
+      <c r="I19" t="s">
         <v>122</v>
       </c>
-      <c r="I15">
-        <v>650</v>
-      </c>
-      <c r="J15" t="s">
+      <c r="J19">
+        <f>650-55</f>
+        <v>595</v>
+      </c>
+      <c r="K19" t="s">
         <v>167</v>
       </c>
-      <c r="K15" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H16" t="s">
-        <v>123</v>
-      </c>
-      <c r="I16">
-        <v>11</v>
-      </c>
-      <c r="J16" t="s">
-        <v>163</v>
-      </c>
-      <c r="K16" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="8:16" x14ac:dyDescent="0.3">
-      <c r="H17" t="s">
-        <v>124</v>
-      </c>
-      <c r="I17">
-        <v>25</v>
-      </c>
-      <c r="J17" t="s">
-        <v>163</v>
-      </c>
-      <c r="K17" t="b">
-        <f>TRUE</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="8:16" x14ac:dyDescent="0.3">
-      <c r="H18" s="3" t="s">
+      <c r="L19" t="b">
+        <v>0</v>
+      </c>
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>170</v>
+      </c>
+      <c r="C20" t="s">
+        <v>172</v>
+      </c>
+      <c r="D20">
+        <f ca="1">SUM(A21:A30)</f>
+        <v>35</v>
+      </c>
+      <c r="H20" s="3">
+        <v>7</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="I18">
-        <v>935</v>
-      </c>
-      <c r="J18" t="s">
+      <c r="J20">
+        <v>900</v>
+      </c>
+      <c r="K20" t="s">
         <v>167</v>
       </c>
-      <c r="K18" t="b">
+      <c r="L20" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="8:16" x14ac:dyDescent="0.3">
-      <c r="P19" s="3"/>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <f ca="1">RANDBETWEEN(1,6)</f>
+        <v>3</v>
+      </c>
+      <c r="C21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D21">
+        <f ca="1">D20/2</f>
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <f t="shared" ref="A22:A30" ca="1" si="0">RANDBETWEEN(1,6)</f>
+        <v>5</v>
+      </c>
+      <c r="C22" t="s">
+        <v>174</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="H27" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I28" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="I29" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="I30" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="H31" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="H32" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="34" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="H34" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="35" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="H35" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="36" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="H36" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="37" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="H37" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="38" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="H38" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="39" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="H39" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="40" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="H40" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="41" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="H41" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="42" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="H42" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="45" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G45" t="s">
+        <v>197</v>
+      </c>
+      <c r="H45" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="46" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G46" t="s">
+        <v>198</v>
+      </c>
+      <c r="H46" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="47" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G47" t="s">
+        <v>200</v>
+      </c>
+      <c r="H47" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="48" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G48" t="s">
+        <v>197</v>
+      </c>
+      <c r="H48" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="49" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G49" t="s">
+        <v>202</v>
+      </c>
+      <c r="H49" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="50" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="H50" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="51" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="H51" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="52" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="H52" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="53" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="H53" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="54" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="H54" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="55" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="H55" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="56" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="H56" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="57" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="H57" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="58" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="H58" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="59" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="H59" t="s">
+        <v>211</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
